--- a/apps/posia_pos/hola2.xlsx
+++ b/apps/posia_pos/hola2.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andyb\ProyectosPersonales2026\POSIA\apps\posia_pos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613951AC-2846-420B-8F18-68BD2DB1E4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851C4EF9-0489-43D1-83C5-EEBDB3B6DC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2FD1370B-7E9C-4C28-BEE4-0F479F36F108}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{2FD1370B-7E9C-4C28-BEE4-0F479F36F108}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Productos Piezas" sheetId="3" r:id="rId2"/>
+    <sheet name="Granel" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="281">
   <si>
     <t>nombre</t>
   </si>
@@ -607,6 +609,276 @@
   </si>
   <si>
     <t>lote_promocion</t>
+  </si>
+  <si>
+    <t>Presentación en gramos</t>
+  </si>
+  <si>
+    <t>Paprika</t>
+  </si>
+  <si>
+    <t>Jalapeño</t>
+  </si>
+  <si>
+    <t>Adobo Fuego</t>
+  </si>
+  <si>
+    <t>Pimentón Naranja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pimentón Rojo </t>
+  </si>
+  <si>
+    <t>Mijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile Martajado </t>
+  </si>
+  <si>
+    <t>Piquín</t>
+  </si>
+  <si>
+    <t>Piquín Entero</t>
+  </si>
+  <si>
+    <t>Mora Azul Miguelito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandía Miguelito </t>
+  </si>
+  <si>
+    <t>Mango Miguelito</t>
+  </si>
+  <si>
+    <t>Fresa Miguelito</t>
+  </si>
+  <si>
+    <t>Tomillo Entero</t>
+  </si>
+  <si>
+    <t>Chile de Árbol Molido</t>
+  </si>
+  <si>
+    <t>Sazonador de Camarón</t>
+  </si>
+  <si>
+    <t>Pepita Rusa</t>
+  </si>
+  <si>
+    <t>Avellana</t>
+  </si>
+  <si>
+    <t>Camarón en Trozos</t>
+  </si>
+  <si>
+    <t>Flaming Hot</t>
+  </si>
+  <si>
+    <t>Haba Molida</t>
+  </si>
+  <si>
+    <t>Dátiles</t>
+  </si>
+  <si>
+    <t>Semila de Calabaza</t>
+  </si>
+  <si>
+    <t>Paprika Española</t>
+  </si>
+  <si>
+    <t>Grenetina</t>
+  </si>
+  <si>
+    <t>Sal Rosa del Himalaya</t>
+  </si>
+  <si>
+    <t>Quinoa</t>
+  </si>
+  <si>
+    <t>Guajillo Molido</t>
+  </si>
+  <si>
+    <t>Pimienta Blanca</t>
+  </si>
+  <si>
+    <t>Tajín</t>
+  </si>
+  <si>
+    <t>Sal Rosa del Himalaya Member's Mark</t>
+  </si>
+  <si>
+    <t>Ajonjolí</t>
+  </si>
+  <si>
+    <t>Semilla de Calabaza con Cáscara</t>
+  </si>
+  <si>
+    <t>Canela Molida</t>
+  </si>
+  <si>
+    <t>Knorr Suiza</t>
+  </si>
+  <si>
+    <t>Chia</t>
+  </si>
+  <si>
+    <t>Carbonato</t>
+  </si>
+  <si>
+    <t>Miguelito</t>
+  </si>
+  <si>
+    <t>Cacahuate Natural Pelado</t>
+  </si>
+  <si>
+    <t>Semilla de Calabaza Chinche</t>
+  </si>
+  <si>
+    <t>Tomillo Molido</t>
+  </si>
+  <si>
+    <t>Cúrcuma</t>
+  </si>
+  <si>
+    <t>Sal Nitro</t>
+  </si>
+  <si>
+    <t>Cacahuate Japonés</t>
+  </si>
+  <si>
+    <t>Pimienta Gorda</t>
+  </si>
+  <si>
+    <t>Comino Molido</t>
+  </si>
+  <si>
+    <t>Pasa Güera</t>
+  </si>
+  <si>
+    <t>Tiburones</t>
+  </si>
+  <si>
+    <t>Granillo Arcoiris</t>
+  </si>
+  <si>
+    <t>Jengibre Molido</t>
+  </si>
+  <si>
+    <t>Clavo Molido</t>
+  </si>
+  <si>
+    <t>Pimienta Blanca Molida</t>
+  </si>
+  <si>
+    <t>Ajonjolí Negro</t>
+  </si>
+  <si>
+    <t>Cacao Molido</t>
+  </si>
+  <si>
+    <t>Cacao Entero</t>
+  </si>
+  <si>
+    <t>Coco Rallado</t>
+  </si>
+  <si>
+    <t>Tapioca</t>
+  </si>
+  <si>
+    <t>Linaza Molida</t>
+  </si>
+  <si>
+    <t>Cebolla Molida</t>
+  </si>
+  <si>
+    <t>Comino Entero</t>
+  </si>
+  <si>
+    <t>Ajo Molido</t>
+  </si>
+  <si>
+    <t>Clavo Entero</t>
+  </si>
+  <si>
+    <t>Frijol de Soya</t>
+  </si>
+  <si>
+    <t>Semilla de Calabaza</t>
+  </si>
+  <si>
+    <t>Girasol Grapiñado</t>
+  </si>
+  <si>
+    <t>Girasol Pelado</t>
+  </si>
+  <si>
+    <t>Arándano</t>
+  </si>
+  <si>
+    <t>Almendra Fileteada</t>
+  </si>
+  <si>
+    <t>Nuez Trozo</t>
+  </si>
+  <si>
+    <t>Chile Mora</t>
+  </si>
+  <si>
+    <t>Almendra</t>
+  </si>
+  <si>
+    <t>Chile Morita</t>
+  </si>
+  <si>
+    <t>Chile Cascabel</t>
+  </si>
+  <si>
+    <t>Pasas</t>
+  </si>
+  <si>
+    <t>Granola Horneada</t>
+  </si>
+  <si>
+    <t>Charal Chapala</t>
+  </si>
+  <si>
+    <t>Ciruela sin Hueso</t>
+  </si>
+  <si>
+    <t>Charal Plateado</t>
+  </si>
+  <si>
+    <t>Bombones con Chocolate</t>
+  </si>
+  <si>
+    <t>Ciruela con Hueso</t>
+  </si>
+  <si>
+    <t>Manguitos</t>
+  </si>
+  <si>
+    <t>Pistache</t>
+  </si>
+  <si>
+    <t>Charal Amarillo</t>
+  </si>
+  <si>
+    <t>Gomitas de Fruta</t>
+  </si>
+  <si>
+    <t>Panditas</t>
+  </si>
+  <si>
+    <t>Miel</t>
+  </si>
+  <si>
+    <t>Piloncillo Mini Tapón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piloncillo Grande </t>
+  </si>
+  <si>
+    <t>Almendra Confitada</t>
   </si>
 </sst>
 </file>
@@ -648,12 +920,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3434,4 +3712,1796 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC142D8C-5646-4E13-8483-14698C4810B2}">
+  <dimension ref="A2:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.26953125" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFCAD5C2-98B0-4936-AD63-6AC168B815E7}">
+  <dimension ref="A1:D185"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.36328125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="20.54296875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="1">
+        <v>250</v>
+      </c>
+      <c r="C2" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="1">
+        <v>100</v>
+      </c>
+      <c r="C4" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="1">
+        <v>250</v>
+      </c>
+      <c r="C5" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="1">
+        <v>100</v>
+      </c>
+      <c r="C6" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>250</v>
+      </c>
+      <c r="C7" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="1">
+        <v>100</v>
+      </c>
+      <c r="C8" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="1">
+        <v>250</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="1">
+        <v>100</v>
+      </c>
+      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="1">
+        <v>250</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100</v>
+      </c>
+      <c r="C12" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
+        <v>250</v>
+      </c>
+      <c r="C13" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="1">
+        <v>250</v>
+      </c>
+      <c r="C14" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C15" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="1">
+        <v>100</v>
+      </c>
+      <c r="C16" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B17" s="1">
+        <v>250</v>
+      </c>
+      <c r="C17" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B18" s="1">
+        <v>250</v>
+      </c>
+      <c r="C18" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C19" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B20" s="1">
+        <v>250</v>
+      </c>
+      <c r="C20" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B21" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C21" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="1">
+        <v>250</v>
+      </c>
+      <c r="C22" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B23" s="1">
+        <v>100</v>
+      </c>
+      <c r="C23" s="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="1">
+        <v>250</v>
+      </c>
+      <c r="C24" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="1">
+        <v>250</v>
+      </c>
+      <c r="C25" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" s="1">
+        <v>100</v>
+      </c>
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B27" s="1">
+        <v>250</v>
+      </c>
+      <c r="C27" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="1">
+        <v>100</v>
+      </c>
+      <c r="C28" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B29" s="1">
+        <v>250</v>
+      </c>
+      <c r="C29" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="1">
+        <v>100</v>
+      </c>
+      <c r="C30" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B31" s="1">
+        <v>250</v>
+      </c>
+      <c r="C31" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B32" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C32" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="1">
+        <v>100</v>
+      </c>
+      <c r="C33" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B34" s="1">
+        <v>250</v>
+      </c>
+      <c r="C34" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" s="1">
+        <v>100</v>
+      </c>
+      <c r="C35" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B36" s="1">
+        <v>250</v>
+      </c>
+      <c r="C36" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" s="1">
+        <v>100</v>
+      </c>
+      <c r="C37" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B38" s="1">
+        <v>250</v>
+      </c>
+      <c r="C38" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B39" s="1">
+        <v>100</v>
+      </c>
+      <c r="C39" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B40" s="1">
+        <v>250</v>
+      </c>
+      <c r="C40" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B41" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C41" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B42" s="1">
+        <v>100</v>
+      </c>
+      <c r="C42" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B43" s="1">
+        <v>250</v>
+      </c>
+      <c r="C43" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B44" s="1">
+        <v>100</v>
+      </c>
+      <c r="C44" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B45" s="1">
+        <v>250</v>
+      </c>
+      <c r="C45" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B46" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C46" s="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B47" s="1">
+        <v>100</v>
+      </c>
+      <c r="C47" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B48" s="1">
+        <v>250</v>
+      </c>
+      <c r="C48" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" s="1">
+        <v>100</v>
+      </c>
+      <c r="C49" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B50" s="1">
+        <v>250</v>
+      </c>
+      <c r="C50" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100</v>
+      </c>
+      <c r="C51" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B52" s="1">
+        <v>250</v>
+      </c>
+      <c r="C52" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B53" s="1">
+        <v>100</v>
+      </c>
+      <c r="C53" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B54" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C54" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B55" s="1">
+        <v>100</v>
+      </c>
+      <c r="C55" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B56" s="1">
+        <v>250</v>
+      </c>
+      <c r="C56" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" s="1">
+        <v>100</v>
+      </c>
+      <c r="C57" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B58" s="1">
+        <v>250</v>
+      </c>
+      <c r="C58" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" s="1">
+        <v>100</v>
+      </c>
+      <c r="C59" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B60" s="1">
+        <v>250</v>
+      </c>
+      <c r="C60" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="1">
+        <v>100</v>
+      </c>
+      <c r="C61" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B62" s="1">
+        <v>250</v>
+      </c>
+      <c r="C62" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B63" s="1">
+        <v>100</v>
+      </c>
+      <c r="C63" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B64" s="1">
+        <v>250</v>
+      </c>
+      <c r="C64" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B65" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C65" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B66" s="1">
+        <v>250</v>
+      </c>
+      <c r="C66" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B67" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C67" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B68" s="1">
+        <v>100</v>
+      </c>
+      <c r="C68" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B69" s="1">
+        <v>250</v>
+      </c>
+      <c r="C69" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="1">
+        <v>250</v>
+      </c>
+      <c r="C70" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B71" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C71" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B72" s="1">
+        <v>100</v>
+      </c>
+      <c r="C72" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B73" s="1">
+        <v>250</v>
+      </c>
+      <c r="C73" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B74" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C74" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" s="1">
+        <v>100</v>
+      </c>
+      <c r="C75" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B76" s="1">
+        <v>250</v>
+      </c>
+      <c r="C76" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B77" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C77" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" s="1">
+        <v>250</v>
+      </c>
+      <c r="C78" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B79" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C79" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B80" s="1">
+        <v>100</v>
+      </c>
+      <c r="C80" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B81" s="1">
+        <v>250</v>
+      </c>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" s="1">
+        <v>100</v>
+      </c>
+      <c r="C82" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B83" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C83" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B84" s="1">
+        <v>100</v>
+      </c>
+      <c r="C84" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B85" s="1">
+        <v>250</v>
+      </c>
+      <c r="C85" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B86" s="1">
+        <v>100</v>
+      </c>
+      <c r="C86" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B87" s="1">
+        <v>250</v>
+      </c>
+      <c r="C87" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B88" s="1">
+        <v>100</v>
+      </c>
+      <c r="C88" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B89" s="1">
+        <v>250</v>
+      </c>
+      <c r="C89" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B90" s="1">
+        <v>100</v>
+      </c>
+      <c r="C90" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B91" s="1">
+        <v>250</v>
+      </c>
+      <c r="C91" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B92" s="1">
+        <v>100</v>
+      </c>
+      <c r="C92" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B93" s="1">
+        <v>250</v>
+      </c>
+      <c r="C93" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B94" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C94" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B95" s="1">
+        <v>100</v>
+      </c>
+      <c r="C95" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B96" s="1">
+        <v>250</v>
+      </c>
+      <c r="C96" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B97" s="1">
+        <v>100</v>
+      </c>
+      <c r="C97" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B98" s="1">
+        <v>250</v>
+      </c>
+      <c r="C98" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B99" s="1">
+        <v>100</v>
+      </c>
+      <c r="C99" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B100" s="1">
+        <v>250</v>
+      </c>
+      <c r="C100" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B101" s="1">
+        <v>100</v>
+      </c>
+      <c r="C101" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B102" s="1">
+        <v>250</v>
+      </c>
+      <c r="C102" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B103" s="1">
+        <v>100</v>
+      </c>
+      <c r="C103" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B104" s="1">
+        <v>250</v>
+      </c>
+      <c r="C104" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B105" s="1">
+        <v>100</v>
+      </c>
+      <c r="C105" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B106" s="1">
+        <v>250</v>
+      </c>
+      <c r="C106" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B107" s="1">
+        <v>100</v>
+      </c>
+      <c r="C107" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B108" s="1">
+        <v>250</v>
+      </c>
+      <c r="C108" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1">
+        <v>100</v>
+      </c>
+      <c r="C109" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B110" s="1">
+        <v>250</v>
+      </c>
+      <c r="C110" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B111" s="1">
+        <v>100</v>
+      </c>
+      <c r="C111" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B112" s="1">
+        <v>250</v>
+      </c>
+      <c r="C112" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B113" s="1">
+        <v>100</v>
+      </c>
+      <c r="C113" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B114" s="1">
+        <v>250</v>
+      </c>
+      <c r="C114" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B115" s="1">
+        <v>100</v>
+      </c>
+      <c r="C115" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B116" s="1">
+        <v>250</v>
+      </c>
+      <c r="C116" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B117" s="1">
+        <v>250</v>
+      </c>
+      <c r="C117" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B118" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C118" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B119" s="1">
+        <v>100</v>
+      </c>
+      <c r="C119" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B120" s="1">
+        <v>250</v>
+      </c>
+      <c r="C120" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B121" s="1">
+        <v>100</v>
+      </c>
+      <c r="C121" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B122" s="1">
+        <v>250</v>
+      </c>
+      <c r="C122" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B123" s="1">
+        <v>100</v>
+      </c>
+      <c r="C123" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B124" s="1">
+        <v>250</v>
+      </c>
+      <c r="C124" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B125" s="1">
+        <v>100</v>
+      </c>
+      <c r="C125" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B126" s="1">
+        <v>250</v>
+      </c>
+      <c r="C126" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B127" s="1">
+        <v>100</v>
+      </c>
+      <c r="C127" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B128" s="1">
+        <v>250</v>
+      </c>
+      <c r="C128" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B129" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C129" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B130" s="1">
+        <v>100</v>
+      </c>
+      <c r="C130" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B131" s="1">
+        <v>100</v>
+      </c>
+      <c r="C131" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B132" s="1">
+        <v>250</v>
+      </c>
+      <c r="C132" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B133" s="1">
+        <v>100</v>
+      </c>
+      <c r="C133" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B134" s="1">
+        <v>250</v>
+      </c>
+      <c r="C134" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B135" s="1">
+        <v>100</v>
+      </c>
+      <c r="C135" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B136" s="1">
+        <v>250</v>
+      </c>
+      <c r="C136" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B137" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C137" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B138" s="1">
+        <v>100</v>
+      </c>
+      <c r="C138" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B139" s="1">
+        <v>250</v>
+      </c>
+      <c r="C139" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B140" s="1">
+        <v>100</v>
+      </c>
+      <c r="C140" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B141" s="1">
+        <v>250</v>
+      </c>
+      <c r="C141" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B142" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C142" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B143" s="1">
+        <v>100</v>
+      </c>
+      <c r="C143" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B144" s="1">
+        <v>250</v>
+      </c>
+      <c r="C144" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B145" s="1">
+        <v>100</v>
+      </c>
+      <c r="C145" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B146" s="1">
+        <v>250</v>
+      </c>
+      <c r="C146" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B147" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C147" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B148" s="1">
+        <v>100</v>
+      </c>
+      <c r="C148" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B149" s="1">
+        <v>250</v>
+      </c>
+      <c r="C149" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B150" s="1">
+        <v>100</v>
+      </c>
+      <c r="C150" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B151" s="1">
+        <v>250</v>
+      </c>
+      <c r="C151" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B152" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C152" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B153" s="1">
+        <v>100</v>
+      </c>
+      <c r="C153" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B154" s="1">
+        <v>250</v>
+      </c>
+      <c r="C154" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B155" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C155" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B156" s="1">
+        <v>250</v>
+      </c>
+      <c r="C156" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B157" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C157" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B158" s="1">
+        <v>100</v>
+      </c>
+      <c r="C158" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B159" s="1">
+        <v>250</v>
+      </c>
+      <c r="C159" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B160" s="1">
+        <v>100</v>
+      </c>
+      <c r="C160" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B161" s="1">
+        <v>250</v>
+      </c>
+      <c r="C161" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B162" s="1">
+        <v>100</v>
+      </c>
+      <c r="C162" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B163" s="1">
+        <v>250</v>
+      </c>
+      <c r="C163" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B164" s="1">
+        <v>100</v>
+      </c>
+      <c r="C164" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B165" s="1">
+        <v>250</v>
+      </c>
+      <c r="C165" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B166" s="1">
+        <v>100</v>
+      </c>
+      <c r="C166" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B167" s="1">
+        <v>250</v>
+      </c>
+      <c r="C167" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B168" s="1">
+        <v>100</v>
+      </c>
+      <c r="C168" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B169" s="1">
+        <v>250</v>
+      </c>
+      <c r="C169" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B170" s="1">
+        <v>100</v>
+      </c>
+      <c r="C170" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B171" s="1">
+        <v>250</v>
+      </c>
+      <c r="C171" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B172" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C172" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B173" s="1">
+        <v>100</v>
+      </c>
+      <c r="C173" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B174" s="1">
+        <v>250</v>
+      </c>
+      <c r="C174" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B175" s="1">
+        <v>100</v>
+      </c>
+      <c r="C175" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B176" s="1">
+        <v>250</v>
+      </c>
+      <c r="C176" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B177" s="1">
+        <v>100</v>
+      </c>
+      <c r="C177" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B178" s="1">
+        <v>250</v>
+      </c>
+      <c r="C178" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B179" s="1">
+        <v>500</v>
+      </c>
+      <c r="C179" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B180" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C180" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B181" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C181" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B182" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C182" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B183" s="1">
+        <v>100</v>
+      </c>
+      <c r="C183" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B184" s="1">
+        <v>250</v>
+      </c>
+      <c r="C184" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B185" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C185" s="1">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/apps/posia_pos/hola2.xlsx
+++ b/apps/posia_pos/hola2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andyb\ProyectosPersonales2026\POSIA\apps\posia_pos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851C4EF9-0489-43D1-83C5-EEBDB3B6DC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CD3282-0C21-4DAE-977C-0188D4326C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{2FD1370B-7E9C-4C28-BEE4-0F479F36F108}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="285">
   <si>
     <t>nombre</t>
   </si>
@@ -879,6 +879,18 @@
   </si>
   <si>
     <t>Almendra Confitada</t>
+  </si>
+  <si>
+    <t>Dulces y Saborizantes</t>
+  </si>
+  <si>
+    <t>Especias y Chiles</t>
+  </si>
+  <si>
+    <t>Semillas</t>
+  </si>
+  <si>
+    <t>Frutos Secos</t>
   </si>
 </sst>
 </file>
@@ -920,7 +932,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -930,9 +942,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3744,7 +3753,7 @@
   <dimension ref="A1:D185"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.36328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="30.36328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" style="1"/>
     <col min="4" max="4" width="20.54296875" style="1" customWidth="1"/>
@@ -3752,7 +3761,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -3766,7 +3775,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>202</v>
       </c>
       <c r="B2" s="1">
@@ -3774,6 +3783,9 @@
       </c>
       <c r="C2" s="1">
         <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -3785,7 +3797,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B4" s="1">
@@ -3794,6 +3806,9 @@
       <c r="C4" s="1">
         <v>15</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
@@ -3804,7 +3819,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>193</v>
       </c>
       <c r="B6" s="1">
@@ -3813,6 +3828,9 @@
       <c r="C6" s="1">
         <v>12</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
@@ -3823,7 +3841,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B8" s="1">
@@ -3832,6 +3850,9 @@
       <c r="C8" s="1">
         <v>12</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" s="1">
@@ -3842,7 +3863,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B10" s="1">
@@ -3851,6 +3872,9 @@
       <c r="C10" s="1">
         <v>10</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B11" s="1">
@@ -3861,7 +3885,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>196</v>
       </c>
       <c r="B12" s="1">
@@ -3870,6 +3894,9 @@
       <c r="C12" s="1">
         <v>15</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B13" s="1">
@@ -3880,7 +3907,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>197</v>
       </c>
       <c r="B14" s="1">
@@ -3888,6 +3915,9 @@
       </c>
       <c r="C14" s="1">
         <v>18</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -3899,7 +3929,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>198</v>
       </c>
       <c r="B16" s="1">
@@ -3908,8 +3938,11 @@
       <c r="C16" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B17" s="1">
         <v>250</v>
       </c>
@@ -3917,8 +3950,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>203</v>
       </c>
       <c r="B18" s="1">
@@ -3927,8 +3960,11 @@
       <c r="C18" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" s="1">
         <v>1000</v>
       </c>
@@ -3936,8 +3972,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>201</v>
       </c>
       <c r="B20" s="1">
@@ -3946,8 +3982,11 @@
       <c r="C20" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B21" s="1">
         <v>1000</v>
       </c>
@@ -3955,8 +3994,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>199</v>
       </c>
       <c r="B22" s="1">
@@ -3965,9 +4004,12 @@
       <c r="C22" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="D22" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>200</v>
       </c>
       <c r="B23" s="1">
@@ -3976,8 +4018,11 @@
       <c r="C23" s="1">
         <v>240</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="1">
         <v>250</v>
       </c>
@@ -3985,8 +4030,8 @@
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B25" s="1">
@@ -3995,9 +4040,12 @@
       <c r="C25" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
+      <c r="D25" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>205</v>
       </c>
       <c r="B26" s="1">
@@ -4006,8 +4054,11 @@
       <c r="C26" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B27" s="1">
         <v>250</v>
       </c>
@@ -4015,8 +4066,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B28" s="1">
@@ -4025,8 +4076,11 @@
       <c r="C28" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" s="1">
         <v>250</v>
       </c>
@@ -4034,8 +4088,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>207</v>
       </c>
       <c r="B30" s="1">
@@ -4044,8 +4098,11 @@
       <c r="C30" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" s="1">
         <v>250</v>
       </c>
@@ -4053,7 +4110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B32" s="1">
         <v>1000</v>
       </c>
@@ -4061,8 +4118,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
         <v>208</v>
       </c>
       <c r="B33" s="1">
@@ -4071,8 +4128,11 @@
       <c r="C33" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B34" s="1">
         <v>250</v>
       </c>
@@ -4080,8 +4140,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
         <v>209</v>
       </c>
       <c r="B35" s="1">
@@ -4090,8 +4150,11 @@
       <c r="C35" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B36" s="1">
         <v>250</v>
       </c>
@@ -4099,8 +4162,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>210</v>
       </c>
       <c r="B37" s="1">
@@ -4109,8 +4172,11 @@
       <c r="C37" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B38" s="1">
         <v>250</v>
       </c>
@@ -4118,8 +4184,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
         <v>211</v>
       </c>
       <c r="B39" s="1">
@@ -4128,8 +4194,11 @@
       <c r="C39" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" s="1">
         <v>250</v>
       </c>
@@ -4137,7 +4206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B41" s="1">
         <v>1000</v>
       </c>
@@ -4145,8 +4214,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B42" s="1">
@@ -4155,8 +4224,11 @@
       <c r="C42" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B43" s="1">
         <v>250</v>
       </c>
@@ -4164,8 +4236,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
         <v>213</v>
       </c>
       <c r="B44" s="1">
@@ -4174,8 +4246,11 @@
       <c r="C44" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B45" s="1">
         <v>250</v>
       </c>
@@ -4183,7 +4258,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" s="1">
         <v>1000</v>
       </c>
@@ -4191,8 +4266,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
         <v>214</v>
       </c>
       <c r="B47" s="1">
@@ -4201,8 +4276,11 @@
       <c r="C47" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B48" s="1">
         <v>250</v>
       </c>
@@ -4210,8 +4288,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>215</v>
       </c>
       <c r="B49" s="1">
@@ -4220,8 +4298,11 @@
       <c r="C49" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B50" s="1">
         <v>250</v>
       </c>
@@ -4229,8 +4310,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
         <v>216</v>
       </c>
       <c r="B51" s="1">
@@ -4239,8 +4320,11 @@
       <c r="C51" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B52" s="1">
         <v>250</v>
       </c>
@@ -4248,8 +4332,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
         <v>217</v>
       </c>
       <c r="B53" s="1">
@@ -4258,8 +4342,11 @@
       <c r="C53" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B54" s="1">
         <v>1000</v>
       </c>
@@ -4267,8 +4354,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
         <v>218</v>
       </c>
       <c r="B55" s="1">
@@ -4277,8 +4364,11 @@
       <c r="C55" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B56" s="1">
         <v>250</v>
       </c>
@@ -4286,8 +4376,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="4" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
         <v>219</v>
       </c>
       <c r="B57" s="1">
@@ -4296,8 +4386,11 @@
       <c r="C57" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B58" s="1">
         <v>250</v>
       </c>
@@ -4305,8 +4398,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="4" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
         <v>220</v>
       </c>
       <c r="B59" s="1">
@@ -4315,8 +4408,11 @@
       <c r="C59" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B60" s="1">
         <v>250</v>
       </c>
@@ -4324,8 +4420,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="4" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B61" s="1">
@@ -4334,8 +4430,11 @@
       <c r="C61" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D61" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B62" s="1">
         <v>250</v>
       </c>
@@ -4343,8 +4442,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="4" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
         <v>223</v>
       </c>
       <c r="B63" s="1">
@@ -4353,8 +4452,11 @@
       <c r="C63" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B64" s="1">
         <v>250</v>
       </c>
@@ -4362,7 +4464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B65" s="1">
         <v>1000</v>
       </c>
@@ -4370,8 +4472,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="4" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
         <v>224</v>
       </c>
       <c r="B66" s="1">
@@ -4380,8 +4482,11 @@
       <c r="C66" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D66" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B67" s="1">
         <v>1000</v>
       </c>
@@ -4389,8 +4494,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="4" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
         <v>225</v>
       </c>
       <c r="B68" s="1">
@@ -4399,8 +4504,11 @@
       <c r="C68" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D68" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B69" s="1">
         <v>250</v>
       </c>
@@ -4408,8 +4516,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="4" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B70" s="1">
@@ -4418,8 +4526,11 @@
       <c r="C70" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D70" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B71" s="1">
         <v>1000</v>
       </c>
@@ -4427,8 +4538,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
         <v>227</v>
       </c>
       <c r="B72" s="1">
@@ -4437,8 +4548,11 @@
       <c r="C72" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B73" s="1">
         <v>250</v>
       </c>
@@ -4446,7 +4560,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B74" s="1">
         <v>1000</v>
       </c>
@@ -4454,8 +4568,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="4" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
         <v>228</v>
       </c>
       <c r="B75" s="1">
@@ -4464,8 +4578,11 @@
       <c r="C75" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D75" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B76" s="1">
         <v>250</v>
       </c>
@@ -4473,7 +4590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B77" s="1">
         <v>1000</v>
       </c>
@@ -4481,8 +4598,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="4" t="s">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
         <v>229</v>
       </c>
       <c r="B78" s="1">
@@ -4491,8 +4608,11 @@
       <c r="C78" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D78" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B79" s="1">
         <v>1000</v>
       </c>
@@ -4500,8 +4620,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="4" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B80" s="1">
@@ -4510,8 +4630,11 @@
       <c r="C80" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D80" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B81" s="1">
         <v>250</v>
       </c>
@@ -4519,8 +4642,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="4" t="s">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
         <v>231</v>
       </c>
       <c r="B82" s="1">
@@ -4529,8 +4652,11 @@
       <c r="C82" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D82" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B83" s="1">
         <v>1000</v>
       </c>
@@ -4538,8 +4664,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="4" t="s">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
         <v>245</v>
       </c>
       <c r="B84" s="1">
@@ -4548,8 +4674,11 @@
       <c r="C84" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D84" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B85" s="1">
         <v>250</v>
       </c>
@@ -4557,8 +4686,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="4" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
         <v>232</v>
       </c>
       <c r="B86" s="1">
@@ -4567,8 +4696,11 @@
       <c r="C86" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D86" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B87" s="1">
         <v>250</v>
       </c>
@@ -4576,8 +4708,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="4" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
         <v>233</v>
       </c>
       <c r="B88" s="1">
@@ -4586,8 +4718,11 @@
       <c r="C88" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D88" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B89" s="1">
         <v>250</v>
       </c>
@@ -4595,8 +4730,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="4" t="s">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
         <v>234</v>
       </c>
       <c r="B90" s="1">
@@ -4605,8 +4740,11 @@
       <c r="C90" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D90" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B91" s="1">
         <v>250</v>
       </c>
@@ -4614,8 +4752,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="4" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
         <v>235</v>
       </c>
       <c r="B92" s="1">
@@ -4624,8 +4762,11 @@
       <c r="C92" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D92" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B93" s="1">
         <v>250</v>
       </c>
@@ -4633,7 +4774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B94" s="1">
         <v>1000</v>
       </c>
@@ -4641,8 +4782,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="4" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B95" s="1">
@@ -4651,8 +4792,11 @@
       <c r="C95" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D95" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B96" s="1">
         <v>250</v>
       </c>
@@ -4660,8 +4804,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="4" t="s">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="1" t="s">
         <v>237</v>
       </c>
       <c r="B97" s="1">
@@ -4670,8 +4814,11 @@
       <c r="C97" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D97" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B98" s="1">
         <v>250</v>
       </c>
@@ -4679,8 +4826,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="4" t="s">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
         <v>238</v>
       </c>
       <c r="B99" s="1">
@@ -4689,8 +4836,11 @@
       <c r="C99" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D99" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B100" s="1">
         <v>250</v>
       </c>
@@ -4698,8 +4848,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="4" t="s">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
         <v>239</v>
       </c>
       <c r="B101" s="1">
@@ -4708,8 +4858,11 @@
       <c r="C101" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D101" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B102" s="1">
         <v>250</v>
       </c>
@@ -4717,8 +4870,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="4" t="s">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
         <v>240</v>
       </c>
       <c r="B103" s="1">
@@ -4727,8 +4880,11 @@
       <c r="C103" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D103" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B104" s="1">
         <v>250</v>
       </c>
@@ -4736,8 +4892,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="4" t="s">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
         <v>241</v>
       </c>
       <c r="B105" s="1">
@@ -4746,8 +4902,11 @@
       <c r="C105" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D105" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B106" s="1">
         <v>250</v>
       </c>
@@ -4755,8 +4914,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="4" t="s">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B107" s="1">
@@ -4765,8 +4924,11 @@
       <c r="C107" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D107" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B108" s="1">
         <v>250</v>
       </c>
@@ -4774,8 +4936,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="4" t="s">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
         <v>243</v>
       </c>
       <c r="B109" s="1">
@@ -4784,8 +4946,11 @@
       <c r="C109" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D109" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B110" s="1">
         <v>250</v>
       </c>
@@ -4793,8 +4958,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="4" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
         <v>244</v>
       </c>
       <c r="B111" s="1">
@@ -4803,8 +4968,11 @@
       <c r="C111" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D111" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B112" s="1">
         <v>250</v>
       </c>
@@ -4812,8 +4980,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="4" t="s">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B113" s="1">
@@ -4822,8 +4990,11 @@
       <c r="C113" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D113" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B114" s="1">
         <v>250</v>
       </c>
@@ -4831,8 +5002,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="4" t="s">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" s="1" t="s">
         <v>247</v>
       </c>
       <c r="B115" s="1">
@@ -4841,8 +5012,11 @@
       <c r="C115" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D115" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B116" s="1">
         <v>250</v>
       </c>
@@ -4850,8 +5024,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="4" t="s">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B117" s="1">
@@ -4860,8 +5034,11 @@
       <c r="C117" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D117" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B118" s="1">
         <v>1000</v>
       </c>
@@ -4869,8 +5046,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="4" t="s">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
         <v>249</v>
       </c>
       <c r="B119" s="1">
@@ -4879,8 +5056,11 @@
       <c r="C119" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D119" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B120" s="1">
         <v>250</v>
       </c>
@@ -4888,8 +5068,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="4" t="s">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
         <v>250</v>
       </c>
       <c r="B121" s="1">
@@ -4898,8 +5078,11 @@
       <c r="C121" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D121" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B122" s="1">
         <v>250</v>
       </c>
@@ -4907,8 +5090,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="4" t="s">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
         <v>251</v>
       </c>
       <c r="B123" s="1">
@@ -4917,8 +5100,11 @@
       <c r="C123" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D123" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B124" s="1">
         <v>250</v>
       </c>
@@ -4926,8 +5112,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" s="4" t="s">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
         <v>252</v>
       </c>
       <c r="B125" s="1">
@@ -4936,8 +5122,11 @@
       <c r="C125" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D125" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B126" s="1">
         <v>250</v>
       </c>
@@ -4945,8 +5134,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" s="4" t="s">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
         <v>253</v>
       </c>
       <c r="B127" s="1">
@@ -4955,8 +5144,11 @@
       <c r="C127" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D127" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B128" s="1">
         <v>250</v>
       </c>
@@ -4964,8 +5156,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" s="4" t="s">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
         <v>254</v>
       </c>
       <c r="B129" s="1">
@@ -4974,9 +5166,12 @@
       <c r="C129" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" s="4" t="s">
+      <c r="D129" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
         <v>255</v>
       </c>
       <c r="B130" s="1">
@@ -4985,9 +5180,12 @@
       <c r="C130" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" s="4" t="s">
+      <c r="D130" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
         <v>256</v>
       </c>
       <c r="B131" s="1">
@@ -4996,8 +5194,11 @@
       <c r="C131" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D131" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B132" s="1">
         <v>250</v>
       </c>
@@ -5005,8 +5206,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" s="4" t="s">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
         <v>257</v>
       </c>
       <c r="B133" s="1">
@@ -5015,8 +5216,11 @@
       <c r="C133" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D133" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B134" s="1">
         <v>250</v>
       </c>
@@ -5024,8 +5228,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" s="4" t="s">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" s="1" t="s">
         <v>258</v>
       </c>
       <c r="B135" s="1">
@@ -5034,8 +5238,11 @@
       <c r="C135" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D135" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B136" s="1">
         <v>250</v>
       </c>
@@ -5043,7 +5250,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B137" s="1">
         <v>1000</v>
       </c>
@@ -5051,8 +5258,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" s="4" t="s">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
         <v>259</v>
       </c>
       <c r="B138" s="1">
@@ -5061,8 +5268,11 @@
       <c r="C138" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D138" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B139" s="1">
         <v>250</v>
       </c>
@@ -5070,8 +5280,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" s="4" t="s">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
         <v>260</v>
       </c>
       <c r="B140" s="1">
@@ -5080,8 +5290,11 @@
       <c r="C140" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D140" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B141" s="1">
         <v>250</v>
       </c>
@@ -5089,7 +5302,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B142" s="1">
         <v>1000</v>
       </c>
@@ -5097,8 +5310,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143" s="4" t="s">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
         <v>261</v>
       </c>
       <c r="B143" s="1">
@@ -5107,8 +5320,11 @@
       <c r="C143" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D143" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B144" s="1">
         <v>250</v>
       </c>
@@ -5116,8 +5332,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145" s="4" t="s">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
         <v>262</v>
       </c>
       <c r="B145" s="1">
@@ -5126,8 +5342,11 @@
       <c r="C145" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D145" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B146" s="1">
         <v>250</v>
       </c>
@@ -5135,7 +5354,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B147" s="1">
         <v>1000</v>
       </c>
@@ -5143,8 +5362,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" s="4" t="s">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
         <v>263</v>
       </c>
       <c r="B148" s="1">
@@ -5153,8 +5372,11 @@
       <c r="C148" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D148" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B149" s="1">
         <v>250</v>
       </c>
@@ -5162,8 +5384,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" s="4" t="s">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B150" s="1">
@@ -5172,8 +5394,11 @@
       <c r="C150" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D150" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B151" s="1">
         <v>250</v>
       </c>
@@ -5181,7 +5406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B152" s="1">
         <v>1000</v>
       </c>
@@ -5189,8 +5414,8 @@
         <v>300</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153" s="4" t="s">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153" s="1" t="s">
         <v>265</v>
       </c>
       <c r="B153" s="1">
@@ -5199,8 +5424,11 @@
       <c r="C153" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D153" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B154" s="1">
         <v>250</v>
       </c>
@@ -5208,7 +5436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B155" s="1">
         <v>1000</v>
       </c>
@@ -5216,8 +5444,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156" s="4" t="s">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
         <v>266</v>
       </c>
       <c r="B156" s="1">
@@ -5226,8 +5454,11 @@
       <c r="C156" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D156" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B157" s="1">
         <v>1000</v>
       </c>
@@ -5235,8 +5466,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" s="4" t="s">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
         <v>267</v>
       </c>
       <c r="B158" s="1">
@@ -5245,8 +5476,11 @@
       <c r="C158" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D158" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B159" s="1">
         <v>250</v>
       </c>
@@ -5254,8 +5488,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160" s="4" t="s">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
         <v>268</v>
       </c>
       <c r="B160" s="1">
@@ -5264,8 +5498,11 @@
       <c r="C160" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D160" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B161" s="1">
         <v>250</v>
       </c>
@@ -5273,8 +5510,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" s="4" t="s">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
         <v>269</v>
       </c>
       <c r="B162" s="1">
@@ -5283,8 +5520,11 @@
       <c r="C162" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D162" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B163" s="1">
         <v>250</v>
       </c>
@@ -5292,8 +5532,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164" s="4" t="s">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B164" s="1">
@@ -5302,8 +5542,11 @@
       <c r="C164" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D164" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B165" s="1">
         <v>250</v>
       </c>
@@ -5311,8 +5554,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166" s="4" t="s">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
         <v>271</v>
       </c>
       <c r="B166" s="1">
@@ -5321,8 +5564,11 @@
       <c r="C166" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D166" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B167" s="1">
         <v>250</v>
       </c>
@@ -5330,8 +5576,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" s="4" t="s">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A168" s="1" t="s">
         <v>272</v>
       </c>
       <c r="B168" s="1">
@@ -5340,8 +5586,11 @@
       <c r="C168" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D168" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B169" s="1">
         <v>250</v>
       </c>
@@ -5349,8 +5598,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" s="4" t="s">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
         <v>273</v>
       </c>
       <c r="B170" s="1">
@@ -5359,8 +5608,11 @@
       <c r="C170" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D170" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B171" s="1">
         <v>250</v>
       </c>
@@ -5368,7 +5620,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B172" s="1">
         <v>1000</v>
       </c>
@@ -5376,8 +5628,8 @@
         <v>300</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A173" s="4" t="s">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" s="1" t="s">
         <v>274</v>
       </c>
       <c r="B173" s="1">
@@ -5386,8 +5638,11 @@
       <c r="C173" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D173" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B174" s="1">
         <v>250</v>
       </c>
@@ -5395,8 +5650,8 @@
         <v>110</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" s="4" t="s">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
         <v>275</v>
       </c>
       <c r="B175" s="1">
@@ -5405,8 +5660,11 @@
       <c r="C175" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D175" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B176" s="1">
         <v>250</v>
       </c>
@@ -5414,8 +5672,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177" s="4" t="s">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
         <v>276</v>
       </c>
       <c r="B177" s="1">
@@ -5424,8 +5682,11 @@
       <c r="C177" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D177" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B178" s="1">
         <v>250</v>
       </c>
@@ -5433,8 +5694,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A179" s="4" t="s">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
         <v>277</v>
       </c>
       <c r="B179" s="1">
@@ -5443,8 +5704,11 @@
       <c r="C179" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D179" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B180" s="1">
         <v>1000</v>
       </c>
@@ -5452,8 +5716,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181" s="4" t="s">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181" s="1" t="s">
         <v>278</v>
       </c>
       <c r="B181" s="1">
@@ -5462,9 +5726,12 @@
       <c r="C181" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" s="4" t="s">
+      <c r="D181" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182" s="1" t="s">
         <v>279</v>
       </c>
       <c r="B182" s="1">
@@ -5473,9 +5740,12 @@
       <c r="C182" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183" s="4" t="s">
+      <c r="D182" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B183" s="1">
@@ -5484,8 +5754,11 @@
       <c r="C183" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D183" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B184" s="1">
         <v>250</v>
       </c>
@@ -5493,7 +5766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B185" s="1">
         <v>1000</v>
       </c>
